--- a/arabic_financial_translator/samples/balance_sheet_ar.xlsx
+++ b/arabic_financial_translator/samples/balance_sheet_ar.xlsx
@@ -426,329 +426,329 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>قائمة المركز المالي الموحدة</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>إيضاح</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>٢٠٢٥</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>٢٠٢٤</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>٢٠٢٥</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>إيضاح</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>قائمة المركز المالي الموحدة</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n"/>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>الأصول</t>
+        </is>
+      </c>
       <c r="B2" s="1" t="n"/>
       <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>الأصول</t>
-        </is>
-      </c>
+      <c r="D2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>النقد والأرصدة لدى البنوك المركزية</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>77746</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>63447</v>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>النقد والأرصدة لدى البنوك المركزية</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>القروض والسلف للبنوك</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>43901</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>43593</v>
       </c>
-      <c r="B4" s="1" t="n">
-        <v>43901</v>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>القروض والسلف للعملاء</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>القروض والسلف للبنوك</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="C5" s="1" t="n">
+        <v>286788</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>281032</v>
       </c>
-      <c r="B5" s="1" t="n">
-        <v>286788</v>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>القروض والسلف للعملاء</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>الاستثمارات في الأوراق المالية</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n">
+        <v>166956</v>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>144556</v>
       </c>
-      <c r="B6" s="1" t="n">
-        <v>166956</v>
-      </c>
-      <c r="C6" s="1" t="n"/>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>الاستثمارات في الأوراق المالية</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>الأدوات المالية المشتقة</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>65782</v>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>81472</v>
       </c>
-      <c r="B7" s="1" t="n">
-        <v>65782</v>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>الأدوات المالية المشتقة</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>الشهرة والأصول غير الملموسة</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>6231</v>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>5791</v>
       </c>
-      <c r="B8" s="1" t="n">
-        <v>6231</v>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>الشهرة والأصول غير الملموسة</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>أصول أخرى</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="1" t="n">
+        <v>67931</v>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>43468</v>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>67931</v>
-      </c>
-      <c r="C9" s="1" t="n"/>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>أصول أخرى</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>إجمالي الأصول</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="n">
+        <v>919955</v>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>849688</v>
       </c>
-      <c r="B10" s="1" t="n">
-        <v>919955</v>
-      </c>
-      <c r="C10" s="1" t="n"/>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>إجمالي الأصول</t>
-        </is>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n"/>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>المطلوبات</t>
+        </is>
+      </c>
       <c r="B11" s="1" t="n"/>
       <c r="C11" s="1" t="n"/>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>المطلوبات</t>
-        </is>
-      </c>
+      <c r="D11" s="1" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ودائع البنوك</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n">
+        <v>30846</v>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>25400</v>
       </c>
-      <c r="B12" s="1" t="n">
-        <v>30846</v>
-      </c>
-      <c r="C12" s="1" t="n"/>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>ودائع البنوك</t>
-        </is>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>حسابات العملاء</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n"/>
+      <c r="C13" s="1" t="n">
+        <v>530161</v>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>464489</v>
       </c>
-      <c r="B13" s="1" t="n">
-        <v>530161</v>
-      </c>
-      <c r="C13" s="1" t="n"/>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>حسابات العملاء</t>
-        </is>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>سندات الدين المصدرة</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>72858</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>64609</v>
       </c>
-      <c r="B14" s="1" t="n">
-        <v>72858</v>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>سندات الدين المصدرة</t>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>المطلوبات الثانوية</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="1" t="n">
+        <v>8834</v>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>10382</v>
       </c>
-      <c r="B15" s="1" t="n">
-        <v>8834</v>
-      </c>
-      <c r="C15" s="1" t="n"/>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>المطلوبات الثانوية</t>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>إجمالي المطلوبات</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n">
+        <v>865369</v>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>798404</v>
       </c>
-      <c r="B16" s="1" t="n">
-        <v>865369</v>
-      </c>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>إجمالي المطلوبات</t>
-        </is>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n"/>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>حقوق الملكية</t>
+        </is>
+      </c>
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="1" t="n"/>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>حقوق الملكية</t>
-        </is>
-      </c>
+      <c r="D17" s="1" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>رأس المال وعلاوة الإصدار</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="1" t="n">
+        <v>6614</v>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>6695</v>
       </c>
-      <c r="B18" s="1" t="n">
-        <v>6614</v>
-      </c>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="inlineStr">
-        <is>
-          <t>رأس المال وعلاوة الإصدار</t>
-        </is>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>احتياطيات أخرى</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n"/>
+      <c r="C19" s="1" t="n">
+        <v>10406</v>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>8724</v>
       </c>
-      <c r="B19" s="1" t="n">
-        <v>10406</v>
-      </c>
-      <c r="C19" s="1" t="n"/>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>احتياطيات أخرى</t>
-        </is>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>الأرباح المبقاة</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n"/>
+      <c r="C20" s="1" t="n">
+        <v>29573</v>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>28969</v>
       </c>
-      <c r="B20" s="1" t="n">
-        <v>29573</v>
-      </c>
-      <c r="C20" s="1" t="n"/>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>الأرباح المبقاة</t>
-        </is>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>إجمالي حقوق الملكية</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n"/>
+      <c r="C21" s="1" t="n">
+        <v>54586</v>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>51284</v>
       </c>
-      <c r="B21" s="1" t="n">
-        <v>54586</v>
-      </c>
-      <c r="C21" s="1" t="n"/>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>إجمالي حقوق الملكية</t>
-        </is>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>إجمالي حقوق الملكية والمطلوبات</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="1" t="n">
+        <v>919955</v>
+      </c>
+      <c r="D22" s="1" t="n">
         <v>849688</v>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>919955</v>
-      </c>
-      <c r="C22" s="1" t="n"/>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>إجمالي حقوق الملكية والمطلوبات</t>
-        </is>
       </c>
     </row>
   </sheetData>
